--- a/docs/layout_design/dwg-2026-10-23/Thach_Bi_Key_Dimensions.xlsx
+++ b/docs/layout_design/dwg-2026-10-23/Thach_Bi_Key_Dimensions.xlsx
@@ -454,8 +454,10 @@
       <x:c r="N3" s="1"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="3" t="str">
-        <x:v>Source: DWG saved 2026-10-23, source file 10; SHA-256 in sheets.json. Millimetres inferred; owner-selected project basis 2026-10-26.</x:v>
+      <x:c r="A4" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Nguồn: DWG lưu 23/10/2026. Đơn vị mm suy từ chuỗi kích thước và nhãn m; INSUNITS=1 (inch, đơn vị chèn). Chờ người thiết kế xác nhận; không tự đổi tỷ lệ.</x:t>
+        </x:is>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -472,8 +474,10 @@
       <x:c r="N4" s="1"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="4" t="str">
-        <x:v>In development / Đang phát triển - Not for construction / Không dùng để thi công</x:v>
+      <x:c r="A5" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Phiên bản 23102026 - Không dùng để thi công</x:t>
+        </x:is>
       </x:c>
       <x:c r="B5" s="1"/>
       <x:c r="C5" s="1"/>
